--- a/artfynd/A 32501-2019 artfynd.xlsx
+++ b/artfynd/A 32501-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1368,6 +1368,414 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114819982</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78453</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488582</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6915779</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114819681</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79504</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488574</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6915778</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114819405</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488583</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6915784</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114819396</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56449</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Frägnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488640</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6915716</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Eliasson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32501-2019 artfynd.xlsx
+++ b/artfynd/A 32501-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
